--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_metropolitana.xlsx
@@ -126,72 +126,72 @@
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Monte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1141,7 +1141,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>13122</v>
+        <v>13119</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1167,7 +1167,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13113</v>
+        <v>13120</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -1180,7 +1180,7 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13301</v>
+        <v>13603</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -1193,7 +1193,7 @@
         <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>13302</v>
+        <v>13601</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1206,7 +1206,7 @@
         <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>13201</v>
+        <v>13113</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>13107</v>
+        <v>13302</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1232,7 +1232,7 @@
         <v>43</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>13401</v>
+        <v>13301</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1245,7 +1245,7 @@
         <v>44</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>13132</v>
+        <v>13124</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -1258,7 +1258,7 @@
         <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13112</v>
+        <v>13107</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -1271,7 +1271,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13114</v>
+        <v>13112</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -1284,7 +1284,7 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13115</v>
+        <v>13201</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -1297,7 +1297,7 @@
         <v>48</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13119</v>
+        <v>13132</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -1310,7 +1310,7 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>13120</v>
+        <v>13125</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -1323,7 +1323,7 @@
         <v>50</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>13124</v>
+        <v>13605</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -1336,7 +1336,7 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13125</v>
+        <v>13602</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -1349,7 +1349,7 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13602</v>
+        <v>13401</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -1362,7 +1362,7 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13605</v>
+        <v>13115</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1375,7 +1375,7 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13601</v>
+        <v>13303</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -1388,7 +1388,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13603</v>
+        <v>13114</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -1401,7 +1401,7 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13303</v>
+        <v>13505</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -1414,7 +1414,7 @@
         <v>57</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>13505</v>
+        <v>13122</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:20</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
